--- a/uploads/Testing2.xlsx
+++ b/uploads/Testing2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9FFC81-BB51-4EAB-A52D-1D0A0DCA0F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7C5B18-5983-4478-893D-111290FFB426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A7A9625-CFEA-4EB9-84B4-F1C908F060B5}"/>
   </bookViews>
@@ -407,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
@@ -486,6 +486,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,7 +1050,9 @@
       <c r="J7" s="4">
         <v>246178317009</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="27">
+        <v>246171063009</v>
+      </c>
       <c r="L7" s="5" t="s">
         <v>6</v>
       </c>
